--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-laboratoire-executant.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-laboratoire-executant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:27:00+00:00</t>
+    <t>2026-04-24T08:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,11 +263,11 @@
     <t>Date de l’exécution</t>
   </si>
   <si>
-    <t>fr-lm-laboratoire-executant.executant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-laboratoire-executant.executant[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Directeur du laboratoire</t>
@@ -585,7 +585,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-laboratoire-executant.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-laboratoire-executant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-laboratoire-executant.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-laboratoire-executant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-laboratoire-executant.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-laboratoire-executant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-laboratoire-executant.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-laboratoire-executant.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
